--- a/data/trans_bre/IP19C07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 19,66</t>
+          <t>-0,39; 19,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 10,2</t>
+          <t>-8,49; 9,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 8,96</t>
+          <t>-11,21; 9,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,88</t>
+          <t>0,0; 15,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,3; —</t>
+          <t>-30,17; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-78,45; 388,43</t>
+          <t>-79,41; 512,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 4,7</t>
+          <t>-3,96; 5,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 3,79</t>
+          <t>-4,82; 3,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,93</t>
+          <t>0,26; 7,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 4,87</t>
+          <t>-2,47; 4,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 64,27</t>
+          <t>-32,44; 66,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 64,19</t>
+          <t>-49,36; 59,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 282,27</t>
+          <t>-1,5; 282,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,52; 138,5</t>
+          <t>-35,87; 115,38</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 14,26</t>
+          <t>-6,49; 12,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 9,27</t>
+          <t>-10,24; 9,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 9,35</t>
+          <t>-6,99; 8,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 11,8</t>
+          <t>-1,4; 12,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,02; 171,19</t>
+          <t>-40,02; 148,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 75,38</t>
+          <t>-46,24; 80,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 143,48</t>
+          <t>-52,7; 125,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 238,93</t>
+          <t>-17,05; 248,4</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 5,99</t>
+          <t>-1,62; 5,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,38</t>
+          <t>-3,7; 3,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 5,7</t>
+          <t>-0,67; 5,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,24</t>
+          <t>-0,94; 5,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 74,04</t>
+          <t>-13,8; 71,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 41,55</t>
+          <t>-31,59; 47,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 130,64</t>
+          <t>-10,35; 134,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 119,51</t>
+          <t>-14,57; 119,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 19,3</t>
+          <t>-0,73; 17,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 9,81</t>
+          <t>-9,23; 10,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 9,21</t>
+          <t>-11,32; 7,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,8</t>
+          <t>0,0; 14,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,17; —</t>
+          <t>-39,69; 1299,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-79,41; 512,44</t>
+          <t>-78,99; 449,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 5,41</t>
+          <t>-3,91; 5,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 3,67</t>
+          <t>-4,36; 2,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 7,15</t>
+          <t>0,27; 6,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,48</t>
+          <t>-2,61; 4,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 66,02</t>
+          <t>-32,37; 64,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 59,98</t>
+          <t>-45,75; 50,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 282,02</t>
+          <t>4,11; 310,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,87; 115,38</t>
+          <t>-37,81; 116,5</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 12,9</t>
+          <t>-5,36; 12,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 9,55</t>
+          <t>-11,87; 7,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 8,89</t>
+          <t>-6,53; 9,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 12,26</t>
+          <t>-1,9; 12,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 148,48</t>
+          <t>-31,86; 176,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 80,4</t>
+          <t>-50,83; 58,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,7; 125,29</t>
+          <t>-48,75; 160,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 248,4</t>
+          <t>-23,6; 244,49</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 5,96</t>
+          <t>-1,33; 5,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,63</t>
+          <t>-3,68; 3,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,6</t>
+          <t>-0,57; 5,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,13</t>
+          <t>-0,93; 5,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 71,75</t>
+          <t>-11,63; 67,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 47,55</t>
+          <t>-32,31; 43,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 134,34</t>
+          <t>-10,83; 126,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 119,18</t>
+          <t>-15,92; 117,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 17,85</t>
+          <t>0,21; 19,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 10,02</t>
+          <t>-8,92; 10,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 7,94</t>
+          <t>-10,82; 8,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,52</t>
+          <t>0,0; 13,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 1299,05</t>
+          <t>-34,3; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-78,99; 449,11</t>
+          <t>-78,45; 388,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 5,26</t>
+          <t>-3,59; 4,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 2,98</t>
+          <t>-4,54; 3,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 6,89</t>
+          <t>0,04; 6,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,5</t>
+          <t>-2,69; 4,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 64,77</t>
+          <t>-30,31; 64,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 50,39</t>
+          <t>-46,79; 64,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 310,0</t>
+          <t>-0,57; 282,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,81; 116,5</t>
+          <t>-35,95; 138,63</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>52,99%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 12,94</t>
+          <t>-5,62; 14,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 7,56</t>
+          <t>-10,62; 9,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 9,61</t>
+          <t>-6,27; 9,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 12,11</t>
+          <t>-2,86; 11,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 176,02</t>
+          <t>-36,02; 171,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,83; 58,87</t>
+          <t>-47,1; 75,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,75; 160,46</t>
+          <t>-49,7; 143,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 244,49</t>
+          <t>-28,01; 218,37</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,87</t>
+          <t>-1,57; 5,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,59</t>
+          <t>-3,53; 3,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,75</t>
+          <t>-0,68; 5,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,24</t>
+          <t>-1,33; 5,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 67,62</t>
+          <t>-13,72; 74,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 43,71</t>
+          <t>-31,73; 41,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 126,84</t>
+          <t>-12,12; 130,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 117,42</t>
+          <t>-19,25; 111,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,42</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,54</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>184,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-40,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>8.415716005418522</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.019834212234425</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.537808377589581</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.74650616857015</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1.839988924246222</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1410377233053914</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.4019492694273567</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +650,160 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,21; 19,66</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,92; 10,2</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,82; 8,96</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,48</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-34,3; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-78,45; 388,43</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.2081569987517171</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.924553868471646</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.82213618424887</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3429584967360009</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.7845394521552956</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>19.66022079545134</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.20153502911131</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.959540515078602</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>13.48079199007125</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>3.884339805557126</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,45</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-6,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>88,95%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,59; 4,7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,54; 3,79</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 6,93</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,69; 4,99</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-30,31; 64,27</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-46,79; 64,19</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-0,57; 282,27</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-35,95; 138,63</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.483929742316512</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.482519982585998</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.452583979131429</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.861494235557736</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04744824645180342</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.06164389169914957</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.8895169854023612</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.150226431457255</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,23</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-4,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>52,99%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.59151740419856</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.54085464557071</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.03727549389689407</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.685930801419478</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3031415232891706</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4678704803356369</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.005729597702659588</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3594554799135588</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,62; 14,26</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,62; 9,27</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,27; 9,35</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,86; 11,31</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-36,02; 171,19</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-47,1; 75,38</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-49,7; 143,48</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-28,01; 218,37</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.701850109846195</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.791436933176848</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.928006722988488</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.987701837622708</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.642732805378602</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.6418515486228631</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2.822721379943721</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.386276894758652</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +811,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,49</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,06%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-2,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.812215692848334</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.8357166100670776</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.01894926354934</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.231330917259989</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.3028704924381802</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.04837292602122477</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.09576811496522636</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.5298582322536731</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 5,99</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,53; 3,38</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,68; 5,7</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 5,24</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-13,72; 74,04</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-31,73; 41,55</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-12,12; 130,64</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-19,25; 111,24</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.618781791611553</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.62283269284609</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.268617705841353</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.863711482659877</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3601822577385291</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4709693670860269</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4970368104475728</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2800506348461969</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>14.25521555180906</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>9.272842319558546</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.349838952894023</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.31264001081184</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.711909519174815</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7537642283284732</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.434807054424125</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.183708963963899</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.209443056719782</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1977556594923366</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.492728158609042</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.887195992232203</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.2206185251206326</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.02002037255755853</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.4390193782586358</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.3117351041317086</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.570491495610452</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.526076092321337</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.6764356033568871</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.32959027572911</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1372428689112504</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3173231347679196</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1211794955182598</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1924690600990381</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.989583073221238</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.377810862091211</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.698356638025405</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.236165758937696</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7404025857937637</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.415499378911945</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.306370642095557</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.112411933945461</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1009,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
